--- a/Result/profitability/5015.xlsx
+++ b/Result/profitability/5015.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.15</v>
       </c>
       <c r="M2" t="n">
-        <v>0.16375</v>
+        <v>0.22</v>
       </c>
       <c r="N2" t="n">
-        <v>17.22625</v>
+        <v>17.51</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0.22</v>
+        <v>0.1025</v>
       </c>
       <c r="N3" t="n">
-        <v>16.38625</v>
+        <v>16.165</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.98</v>
       </c>
       <c r="M4" t="n">
-        <v>0.18375</v>
+        <v>0.16375</v>
       </c>
       <c r="N4" t="n">
-        <v>14.8</v>
+        <v>15.26875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1425</v>
+        <v>0.355</v>
       </c>
       <c r="N5" t="n">
-        <v>14.22625</v>
+        <v>14.81875</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>0.35375</v>
+        <v>0.32875</v>
       </c>
       <c r="N6" t="n">
-        <v>14.1075</v>
+        <v>15.125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2537499999999999</v>
+        <v>0.24375</v>
       </c>
       <c r="N7" t="n">
-        <v>13.44875</v>
+        <v>14.20875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="N8" t="n">
-        <v>12.8675</v>
+        <v>13.355</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5015</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>320</v>
+      </c>
+      <c r="D75" t="n">
+        <v>249</v>
+      </c>
+      <c r="E75" t="n">
+        <v>71</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="G75" t="n">
+        <v>22</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.83%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>27</v>
+      </c>
+      <c r="K75" t="n">
+        <v>20</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2237499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.86125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.899999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2125340599455039</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.240875912408759</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.739999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2707024557395772</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
